--- a/data/법정동 기준 시군구 단위.xlsx
+++ b/data/법정동 기준 시군구 단위.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\SKN10-FINAL-5Team\Data\EDA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\SKN10-FINAL-5Team\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65CAF40A-EBDC-44A9-A3BA-AA3D850F18A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA47D71-0EDA-4250-85AD-BD1B3B6F545D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{24CA9D51-535D-4E78-9AC6-608F6317D634}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{24CA9D51-535D-4E78-9AC6-608F6317D634}"/>
   </bookViews>
   <sheets>
     <sheet name="통합 버전_with시도" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="530">
   <si>
     <t>서울특별시</t>
   </si>
@@ -1138,60 +1138,6 @@
     <t>경기도 화성시</t>
   </si>
   <si>
-    <t>강원도 강릉시</t>
-  </si>
-  <si>
-    <t>강원도 고성군</t>
-  </si>
-  <si>
-    <t>강원도 동해시</t>
-  </si>
-  <si>
-    <t>강원도 삼척시</t>
-  </si>
-  <si>
-    <t>강원도 속초시</t>
-  </si>
-  <si>
-    <t>강원도 양구군</t>
-  </si>
-  <si>
-    <t>강원도 양양군</t>
-  </si>
-  <si>
-    <t>강원도 영월군</t>
-  </si>
-  <si>
-    <t>강원도 원주시</t>
-  </si>
-  <si>
-    <t>강원도 인제군</t>
-  </si>
-  <si>
-    <t>강원도 정선군</t>
-  </si>
-  <si>
-    <t>강원도 철원군</t>
-  </si>
-  <si>
-    <t>강원도 춘천시</t>
-  </si>
-  <si>
-    <t>강원도 태백시</t>
-  </si>
-  <si>
-    <t>강원도 평창군</t>
-  </si>
-  <si>
-    <t>강원도 홍천군</t>
-  </si>
-  <si>
-    <t>강원도 화천군</t>
-  </si>
-  <si>
-    <t>강원도 횡성군</t>
-  </si>
-  <si>
     <t>충청북도 괴산군</t>
   </si>
   <si>
@@ -1280,51 +1226,6 @@
   </si>
   <si>
     <t>충청남도 홍성군</t>
-  </si>
-  <si>
-    <t>전라북도 고창군</t>
-  </si>
-  <si>
-    <t>전라북도 군산시</t>
-  </si>
-  <si>
-    <t>전라북도 김제시</t>
-  </si>
-  <si>
-    <t>전라북도 남원시</t>
-  </si>
-  <si>
-    <t>전라북도 무주군</t>
-  </si>
-  <si>
-    <t>전라북도 부안군</t>
-  </si>
-  <si>
-    <t>전라북도 순창군</t>
-  </si>
-  <si>
-    <t>전라북도 완주군</t>
-  </si>
-  <si>
-    <t>전라북도 익산시</t>
-  </si>
-  <si>
-    <t>전라북도 임실군</t>
-  </si>
-  <si>
-    <t>전라북도 장수군</t>
-  </si>
-  <si>
-    <t>전라북도 전주시 덕진구</t>
-  </si>
-  <si>
-    <t>전라북도 전주시 완산구</t>
-  </si>
-  <si>
-    <t>전라북도 정읍시</t>
-  </si>
-  <si>
-    <t>전라북도 진안군</t>
   </si>
   <si>
     <t>전라남도 강진군</t>
@@ -1640,6 +1541,127 @@
   </si>
   <si>
     <t>전북특별자치도 고창군</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 강남구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 강동구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강원도 강릉시</t>
+  </si>
+  <si>
+    <t>강원도 고성군</t>
+  </si>
+  <si>
+    <t>강원도 동해시</t>
+  </si>
+  <si>
+    <t>강원도 삼척시</t>
+  </si>
+  <si>
+    <t>강원도 속초시</t>
+  </si>
+  <si>
+    <t>강원도 양구군</t>
+  </si>
+  <si>
+    <t>강원도 양양군</t>
+  </si>
+  <si>
+    <t>강원도 영월군</t>
+  </si>
+  <si>
+    <t>강원도 원주시</t>
+  </si>
+  <si>
+    <t>강원도 인제군</t>
+  </si>
+  <si>
+    <t>강원도 정선군</t>
+  </si>
+  <si>
+    <t>강원도 철원군</t>
+  </si>
+  <si>
+    <t>강원도 춘천시</t>
+  </si>
+  <si>
+    <t>강원도 태백시</t>
+  </si>
+  <si>
+    <t>강원도 평창군</t>
+  </si>
+  <si>
+    <t>강원도 홍천군</t>
+  </si>
+  <si>
+    <t>강원도 화천군</t>
+  </si>
+  <si>
+    <t>강원도 횡성군</t>
+  </si>
+  <si>
+    <t>전라북도 고창군</t>
+  </si>
+  <si>
+    <t>전라북도 군산시</t>
+  </si>
+  <si>
+    <t>전라북도 김제시</t>
+  </si>
+  <si>
+    <t>전라북도 남원시</t>
+  </si>
+  <si>
+    <t>전라북도 무주군</t>
+  </si>
+  <si>
+    <t>전라북도 부안군</t>
+  </si>
+  <si>
+    <t>전라북도 순창군</t>
+  </si>
+  <si>
+    <t>전라북도 완주군</t>
+  </si>
+  <si>
+    <t>전라북도 익산시</t>
+  </si>
+  <si>
+    <t>전라북도 임실군</t>
+  </si>
+  <si>
+    <t>전라북도 장수군</t>
+  </si>
+  <si>
+    <t>전라북도 전주시 덕진구</t>
+  </si>
+  <si>
+    <t>전라북도 전주시 완산구</t>
+  </si>
+  <si>
+    <t>전라북도 정읍시</t>
+  </si>
+  <si>
+    <t>전라북도 진안군</t>
+  </si>
+  <si>
+    <t>제주 서귀포시</t>
+  </si>
+  <si>
+    <t>제주 제주시</t>
+  </si>
+  <si>
+    <t>부산 남구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부산 부산진구</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4039,7 +4061,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>247</v>
+        <v>491</v>
       </c>
       <c r="B2">
         <v>11680</v>
@@ -4047,7 +4069,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>248</v>
+        <v>492</v>
       </c>
       <c r="B3">
         <v>11740</v>
@@ -4263,7 +4285,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>275</v>
+        <v>528</v>
       </c>
       <c r="B30">
         <v>26290</v>
@@ -4287,7 +4309,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>278</v>
+        <v>529</v>
       </c>
       <c r="B33">
         <v>26230</v>
@@ -4975,7 +4997,7 @@
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>364</v>
+        <v>493</v>
       </c>
       <c r="B119">
         <v>42150</v>
@@ -4983,7 +5005,7 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>365</v>
+        <v>494</v>
       </c>
       <c r="B120">
         <v>42820</v>
@@ -4991,7 +5013,7 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>366</v>
+        <v>495</v>
       </c>
       <c r="B121">
         <v>42170</v>
@@ -4999,7 +5021,7 @@
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>367</v>
+        <v>496</v>
       </c>
       <c r="B122">
         <v>42230</v>
@@ -5007,7 +5029,7 @@
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>368</v>
+        <v>497</v>
       </c>
       <c r="B123">
         <v>42210</v>
@@ -5015,7 +5037,7 @@
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>369</v>
+        <v>498</v>
       </c>
       <c r="B124">
         <v>42800</v>
@@ -5023,7 +5045,7 @@
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>370</v>
+        <v>499</v>
       </c>
       <c r="B125">
         <v>42830</v>
@@ -5031,7 +5053,7 @@
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>371</v>
+        <v>500</v>
       </c>
       <c r="B126">
         <v>42750</v>
@@ -5039,7 +5061,7 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>372</v>
+        <v>501</v>
       </c>
       <c r="B127">
         <v>42130</v>
@@ -5047,7 +5069,7 @@
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>373</v>
+        <v>502</v>
       </c>
       <c r="B128">
         <v>42810</v>
@@ -5055,7 +5077,7 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>374</v>
+        <v>503</v>
       </c>
       <c r="B129">
         <v>42770</v>
@@ -5063,7 +5085,7 @@
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>375</v>
+        <v>504</v>
       </c>
       <c r="B130">
         <v>42780</v>
@@ -5071,7 +5093,7 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>376</v>
+        <v>505</v>
       </c>
       <c r="B131">
         <v>42110</v>
@@ -5079,7 +5101,7 @@
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>377</v>
+        <v>506</v>
       </c>
       <c r="B132">
         <v>42190</v>
@@ -5087,7 +5109,7 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>378</v>
+        <v>507</v>
       </c>
       <c r="B133">
         <v>42760</v>
@@ -5095,7 +5117,7 @@
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>379</v>
+        <v>508</v>
       </c>
       <c r="B134">
         <v>42720</v>
@@ -5103,7 +5125,7 @@
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>380</v>
+        <v>509</v>
       </c>
       <c r="B135">
         <v>42790</v>
@@ -5111,7 +5133,7 @@
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>381</v>
+        <v>510</v>
       </c>
       <c r="B136">
         <v>42730</v>
@@ -5119,7 +5141,7 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
       <c r="B137">
         <v>43760</v>
@@ -5127,7 +5149,7 @@
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="B138">
         <v>43800</v>
@@ -5135,7 +5157,7 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
       <c r="B139">
         <v>43720</v>
@@ -5143,7 +5165,7 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="B140">
         <v>43740</v>
@@ -5151,7 +5173,7 @@
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="B141">
         <v>43730</v>
@@ -5159,7 +5181,7 @@
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="B142">
         <v>43770</v>
@@ -5167,7 +5189,7 @@
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="B143">
         <v>43150</v>
@@ -5175,7 +5197,7 @@
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="B144">
         <v>43745</v>
@@ -5183,7 +5205,7 @@
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="B145">
         <v>43750</v>
@@ -5191,7 +5213,7 @@
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="B146">
         <v>43111</v>
@@ -5199,7 +5221,7 @@
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="B147">
         <v>43112</v>
@@ -5207,7 +5229,7 @@
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>393</v>
+        <v>375</v>
       </c>
       <c r="B148">
         <v>43114</v>
@@ -5215,7 +5237,7 @@
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
       <c r="B149">
         <v>43113</v>
@@ -5223,7 +5245,7 @@
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="B150">
         <v>43130</v>
@@ -5231,7 +5253,7 @@
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="B151">
         <v>44250</v>
@@ -5239,7 +5261,7 @@
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="B152">
         <v>44150</v>
@@ -5247,7 +5269,7 @@
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
       <c r="B153">
         <v>44710</v>
@@ -5255,7 +5277,7 @@
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="B154">
         <v>44230</v>
@@ -5263,7 +5285,7 @@
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="B155">
         <v>44270</v>
@@ -5271,7 +5293,7 @@
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>401</v>
+        <v>383</v>
       </c>
       <c r="B156">
         <v>44180</v>
@@ -5279,7 +5301,7 @@
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="B157">
         <v>44760</v>
@@ -5287,7 +5309,7 @@
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>403</v>
+        <v>385</v>
       </c>
       <c r="B158">
         <v>44210</v>
@@ -5295,7 +5317,7 @@
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>404</v>
+        <v>386</v>
       </c>
       <c r="B159">
         <v>44770</v>
@@ -5303,7 +5325,7 @@
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>405</v>
+        <v>387</v>
       </c>
       <c r="B160">
         <v>44200</v>
@@ -5311,7 +5333,7 @@
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>406</v>
+        <v>388</v>
       </c>
       <c r="B161">
         <v>44810</v>
@@ -5319,7 +5341,7 @@
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>407</v>
+        <v>389</v>
       </c>
       <c r="B162">
         <v>44131</v>
@@ -5327,7 +5349,7 @@
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>408</v>
+        <v>390</v>
       </c>
       <c r="B163">
         <v>44133</v>
@@ -5335,7 +5357,7 @@
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>409</v>
+        <v>391</v>
       </c>
       <c r="B164">
         <v>44790</v>
@@ -5343,7 +5365,7 @@
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>410</v>
+        <v>392</v>
       </c>
       <c r="B165">
         <v>44825</v>
@@ -5351,7 +5373,7 @@
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>411</v>
+        <v>393</v>
       </c>
       <c r="B166">
         <v>44800</v>
@@ -5359,7 +5381,7 @@
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>412</v>
+        <v>511</v>
       </c>
       <c r="B167">
         <v>45790</v>
@@ -5367,7 +5389,7 @@
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>413</v>
+        <v>512</v>
       </c>
       <c r="B168">
         <v>45130</v>
@@ -5375,7 +5397,7 @@
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>414</v>
+        <v>513</v>
       </c>
       <c r="B169">
         <v>45210</v>
@@ -5383,7 +5405,7 @@
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>415</v>
+        <v>514</v>
       </c>
       <c r="B170">
         <v>45190</v>
@@ -5391,7 +5413,7 @@
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>416</v>
+        <v>515</v>
       </c>
       <c r="B171">
         <v>45730</v>
@@ -5399,7 +5421,7 @@
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>417</v>
+        <v>516</v>
       </c>
       <c r="B172">
         <v>45800</v>
@@ -5407,7 +5429,7 @@
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>418</v>
+        <v>517</v>
       </c>
       <c r="B173">
         <v>45770</v>
@@ -5415,7 +5437,7 @@
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>419</v>
+        <v>518</v>
       </c>
       <c r="B174">
         <v>45710</v>
@@ -5423,7 +5445,7 @@
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>420</v>
+        <v>519</v>
       </c>
       <c r="B175">
         <v>45140</v>
@@ -5431,7 +5453,7 @@
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>421</v>
+        <v>520</v>
       </c>
       <c r="B176">
         <v>45750</v>
@@ -5439,7 +5461,7 @@
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>422</v>
+        <v>521</v>
       </c>
       <c r="B177">
         <v>45740</v>
@@ -5447,7 +5469,7 @@
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>423</v>
+        <v>522</v>
       </c>
       <c r="B178">
         <v>45113</v>
@@ -5455,7 +5477,7 @@
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>424</v>
+        <v>523</v>
       </c>
       <c r="B179">
         <v>45111</v>
@@ -5463,7 +5485,7 @@
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>425</v>
+        <v>524</v>
       </c>
       <c r="B180">
         <v>45180</v>
@@ -5471,7 +5493,7 @@
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>426</v>
+        <v>525</v>
       </c>
       <c r="B181">
         <v>45720</v>
@@ -5479,7 +5501,7 @@
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>427</v>
+        <v>394</v>
       </c>
       <c r="B182">
         <v>46810</v>
@@ -5487,7 +5509,7 @@
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>428</v>
+        <v>395</v>
       </c>
       <c r="B183">
         <v>46770</v>
@@ -5495,7 +5517,7 @@
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>429</v>
+        <v>396</v>
       </c>
       <c r="B184">
         <v>46720</v>
@@ -5503,7 +5525,7 @@
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>430</v>
+        <v>397</v>
       </c>
       <c r="B185">
         <v>46230</v>
@@ -5511,7 +5533,7 @@
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>431</v>
+        <v>398</v>
       </c>
       <c r="B186">
         <v>46730</v>
@@ -5519,7 +5541,7 @@
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>432</v>
+        <v>399</v>
       </c>
       <c r="B187">
         <v>46170</v>
@@ -5527,7 +5549,7 @@
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>433</v>
+        <v>400</v>
       </c>
       <c r="B188">
         <v>46710</v>
@@ -5535,7 +5557,7 @@
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>434</v>
+        <v>401</v>
       </c>
       <c r="B189">
         <v>46110</v>
@@ -5543,7 +5565,7 @@
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>435</v>
+        <v>402</v>
       </c>
       <c r="B190">
         <v>46840</v>
@@ -5551,7 +5573,7 @@
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>436</v>
+        <v>403</v>
       </c>
       <c r="B191">
         <v>46780</v>
@@ -5559,7 +5581,7 @@
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>437</v>
+        <v>404</v>
       </c>
       <c r="B192">
         <v>46150</v>
@@ -5567,7 +5589,7 @@
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>438</v>
+        <v>405</v>
       </c>
       <c r="B193">
         <v>46910</v>
@@ -5575,7 +5597,7 @@
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>439</v>
+        <v>406</v>
       </c>
       <c r="B194">
         <v>46130</v>
@@ -5583,7 +5605,7 @@
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>440</v>
+        <v>407</v>
       </c>
       <c r="B195">
         <v>46870</v>
@@ -5591,7 +5613,7 @@
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>441</v>
+        <v>408</v>
       </c>
       <c r="B196">
         <v>46830</v>
@@ -5599,7 +5621,7 @@
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>442</v>
+        <v>409</v>
       </c>
       <c r="B197">
         <v>46890</v>
@@ -5607,7 +5629,7 @@
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>443</v>
+        <v>410</v>
       </c>
       <c r="B198">
         <v>46880</v>
@@ -5615,7 +5637,7 @@
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>444</v>
+        <v>411</v>
       </c>
       <c r="B199">
         <v>46800</v>
@@ -5623,7 +5645,7 @@
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>445</v>
+        <v>412</v>
       </c>
       <c r="B200">
         <v>46900</v>
@@ -5631,7 +5653,7 @@
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>446</v>
+        <v>413</v>
       </c>
       <c r="B201">
         <v>46860</v>
@@ -5639,7 +5661,7 @@
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>447</v>
+        <v>414</v>
       </c>
       <c r="B202">
         <v>46820</v>
@@ -5647,7 +5669,7 @@
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>448</v>
+        <v>415</v>
       </c>
       <c r="B203">
         <v>46790</v>
@@ -5655,7 +5677,7 @@
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>449</v>
+        <v>416</v>
       </c>
       <c r="B204">
         <v>47290</v>
@@ -5663,7 +5685,7 @@
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>450</v>
+        <v>417</v>
       </c>
       <c r="B205">
         <v>47130</v>
@@ -5671,7 +5693,7 @@
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>451</v>
+        <v>418</v>
       </c>
       <c r="B206">
         <v>47830</v>
@@ -5679,7 +5701,7 @@
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>452</v>
+        <v>419</v>
       </c>
       <c r="B207">
         <v>47190</v>
@@ -5687,7 +5709,7 @@
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>453</v>
+        <v>420</v>
       </c>
       <c r="B208">
         <v>47720</v>
@@ -5695,7 +5717,7 @@
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>454</v>
+        <v>421</v>
       </c>
       <c r="B209">
         <v>47150</v>
@@ -5703,7 +5725,7 @@
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>455</v>
+        <v>422</v>
       </c>
       <c r="B210">
         <v>47280</v>
@@ -5711,7 +5733,7 @@
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>456</v>
+        <v>423</v>
       </c>
       <c r="B211">
         <v>47920</v>
@@ -5719,7 +5741,7 @@
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>457</v>
+        <v>424</v>
       </c>
       <c r="B212">
         <v>47250</v>
@@ -5727,7 +5749,7 @@
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>458</v>
+        <v>425</v>
       </c>
       <c r="B213">
         <v>47840</v>
@@ -5735,7 +5757,7 @@
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>459</v>
+        <v>426</v>
       </c>
       <c r="B214">
         <v>47170</v>
@@ -5743,7 +5765,7 @@
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>460</v>
+        <v>427</v>
       </c>
       <c r="B215">
         <v>47770</v>
@@ -5751,7 +5773,7 @@
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>461</v>
+        <v>428</v>
       </c>
       <c r="B216">
         <v>47760</v>
@@ -5759,7 +5781,7 @@
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>462</v>
+        <v>429</v>
       </c>
       <c r="B217">
         <v>47210</v>
@@ -5767,7 +5789,7 @@
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>463</v>
+        <v>430</v>
       </c>
       <c r="B218">
         <v>47230</v>
@@ -5775,7 +5797,7 @@
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>464</v>
+        <v>431</v>
       </c>
       <c r="B219">
         <v>47900</v>
@@ -5783,7 +5805,7 @@
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>465</v>
+        <v>432</v>
       </c>
       <c r="B220">
         <v>47940</v>
@@ -5791,7 +5813,7 @@
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>466</v>
+        <v>433</v>
       </c>
       <c r="B221">
         <v>47930</v>
@@ -5799,7 +5821,7 @@
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>467</v>
+        <v>434</v>
       </c>
       <c r="B222">
         <v>47730</v>
@@ -5807,7 +5829,7 @@
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>468</v>
+        <v>435</v>
       </c>
       <c r="B223">
         <v>47820</v>
@@ -5815,7 +5837,7 @@
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>469</v>
+        <v>436</v>
       </c>
       <c r="B224">
         <v>47750</v>
@@ -5823,7 +5845,7 @@
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>470</v>
+        <v>437</v>
       </c>
       <c r="B225">
         <v>47850</v>
@@ -5831,7 +5853,7 @@
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>471</v>
+        <v>438</v>
       </c>
       <c r="B226">
         <v>47111</v>
@@ -5839,7 +5861,7 @@
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="B227">
         <v>47113</v>
@@ -5847,7 +5869,7 @@
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>473</v>
+        <v>440</v>
       </c>
       <c r="B228">
         <v>48310</v>
@@ -5855,7 +5877,7 @@
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="B229">
         <v>48880</v>
@@ -5863,7 +5885,7 @@
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>475</v>
+        <v>442</v>
       </c>
       <c r="B230">
         <v>48820</v>
@@ -5871,7 +5893,7 @@
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>476</v>
+        <v>443</v>
       </c>
       <c r="B231">
         <v>48250</v>
@@ -5879,7 +5901,7 @@
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>477</v>
+        <v>444</v>
       </c>
       <c r="B232">
         <v>48840</v>
@@ -5887,7 +5909,7 @@
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>478</v>
+        <v>445</v>
       </c>
       <c r="B233">
         <v>48270</v>
@@ -5895,7 +5917,7 @@
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="B234">
         <v>48240</v>
@@ -5903,7 +5925,7 @@
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>480</v>
+        <v>447</v>
       </c>
       <c r="B235">
         <v>48860</v>
@@ -5911,7 +5933,7 @@
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>481</v>
+        <v>448</v>
       </c>
       <c r="B236">
         <v>48330</v>
@@ -5919,7 +5941,7 @@
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>482</v>
+        <v>449</v>
       </c>
       <c r="B237">
         <v>48720</v>
@@ -5927,7 +5949,7 @@
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="B238">
         <v>48170</v>
@@ -5935,7 +5957,7 @@
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="B239">
         <v>48740</v>
@@ -5943,7 +5965,7 @@
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>485</v>
+        <v>452</v>
       </c>
       <c r="B240">
         <v>48125</v>
@@ -5951,7 +5973,7 @@
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>486</v>
+        <v>453</v>
       </c>
       <c r="B241">
         <v>48127</v>
@@ -5959,7 +5981,7 @@
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>487</v>
+        <v>454</v>
       </c>
       <c r="B242">
         <v>48123</v>
@@ -5967,7 +5989,7 @@
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>488</v>
+        <v>455</v>
       </c>
       <c r="B243">
         <v>48121</v>
@@ -5975,7 +5997,7 @@
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>489</v>
+        <v>456</v>
       </c>
       <c r="B244">
         <v>48129</v>
@@ -5983,7 +6005,7 @@
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>490</v>
+        <v>457</v>
       </c>
       <c r="B245">
         <v>48220</v>
@@ -5991,7 +6013,7 @@
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>491</v>
+        <v>458</v>
       </c>
       <c r="B246">
         <v>48850</v>
@@ -5999,7 +6021,7 @@
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>492</v>
+        <v>459</v>
       </c>
       <c r="B247">
         <v>48730</v>
@@ -6007,7 +6029,7 @@
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>496</v>
+        <v>463</v>
       </c>
       <c r="B248">
         <v>48870</v>
@@ -6015,7 +6037,7 @@
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>493</v>
+        <v>460</v>
       </c>
       <c r="B249">
         <v>48890</v>
@@ -6023,7 +6045,7 @@
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>494</v>
+        <v>526</v>
       </c>
       <c r="B250">
         <v>50130</v>
@@ -6031,7 +6053,7 @@
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>495</v>
+        <v>527</v>
       </c>
       <c r="B251">
         <v>50110</v>
@@ -8601,7 +8623,7 @@
         <v>48220</v>
       </c>
       <c r="G281" t="s">
-        <v>497</v>
+        <v>464</v>
       </c>
       <c r="H281">
         <v>52000</v>
@@ -8643,7 +8665,7 @@
         <v>48870</v>
       </c>
       <c r="G284" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="H284">
         <v>41110</v>
@@ -8679,7 +8701,7 @@
         <v>245</v>
       </c>
       <c r="G287" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="H287">
         <v>48120</v>
@@ -8687,13 +8709,13 @@
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>494</v>
+        <v>461</v>
       </c>
       <c r="B288">
         <v>50130</v>
       </c>
       <c r="G288" t="s">
-        <v>500</v>
+        <v>467</v>
       </c>
       <c r="H288">
         <v>47000</v>
@@ -8701,13 +8723,13 @@
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>495</v>
+        <v>462</v>
       </c>
       <c r="B289">
         <v>50110</v>
       </c>
       <c r="G289" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="H289">
         <v>41130</v>
@@ -8715,7 +8737,7 @@
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G290" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="H290">
         <v>41280</v>
@@ -8723,7 +8745,7 @@
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G291" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="H291">
         <v>41170</v>
@@ -8731,7 +8753,7 @@
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G292" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="H292">
         <v>41460</v>
@@ -8739,7 +8761,7 @@
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G293" t="s">
-        <v>505</v>
+        <v>472</v>
       </c>
       <c r="H293">
         <v>30000</v>
@@ -8747,7 +8769,7 @@
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G294" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="H294">
         <v>44000</v>
@@ -8755,7 +8777,7 @@
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G295" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="H295">
         <v>51000</v>
@@ -8763,7 +8785,7 @@
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G296" t="s">
-        <v>508</v>
+        <v>475</v>
       </c>
       <c r="H296">
         <v>52140</v>
@@ -8771,7 +8793,7 @@
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G297" t="s">
-        <v>509</v>
+        <v>476</v>
       </c>
       <c r="H297">
         <v>43000</v>
@@ -8779,7 +8801,7 @@
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G298" t="s">
-        <v>510</v>
+        <v>477</v>
       </c>
       <c r="H298">
         <v>52110</v>
@@ -8787,7 +8809,7 @@
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G299" t="s">
-        <v>511</v>
+        <v>478</v>
       </c>
       <c r="H299">
         <v>51130</v>
@@ -8795,7 +8817,7 @@
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G300" t="s">
-        <v>512</v>
+        <v>479</v>
       </c>
       <c r="H300">
         <v>52130</v>
@@ -8803,7 +8825,7 @@
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G301" t="s">
-        <v>513</v>
+        <v>480</v>
       </c>
       <c r="H301">
         <v>41270</v>
@@ -8811,7 +8833,7 @@
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G302" t="s">
-        <v>514</v>
+        <v>481</v>
       </c>
       <c r="H302">
         <v>46000</v>
@@ -8819,7 +8841,7 @@
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G303" t="s">
-        <v>515</v>
+        <v>482</v>
       </c>
       <c r="H303">
         <v>52210</v>
@@ -8827,7 +8849,7 @@
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G304" t="s">
-        <v>516</v>
+        <v>483</v>
       </c>
       <c r="H304">
         <v>52770</v>
@@ -8835,12 +8857,12 @@
     </row>
     <row r="305" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G305" t="s">
-        <v>517</v>
+        <v>484</v>
       </c>
     </row>
     <row r="306" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G306" t="s">
-        <v>518</v>
+        <v>485</v>
       </c>
       <c r="H306">
         <v>52710</v>
@@ -8848,7 +8870,7 @@
     </row>
     <row r="307" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G307" t="s">
-        <v>519</v>
+        <v>486</v>
       </c>
       <c r="H307">
         <v>52190</v>
@@ -8856,7 +8878,7 @@
     </row>
     <row r="308" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G308" t="s">
-        <v>520</v>
+        <v>487</v>
       </c>
       <c r="H308">
         <v>52180</v>
@@ -8864,7 +8886,7 @@
     </row>
     <row r="309" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G309" t="s">
-        <v>521</v>
+        <v>488</v>
       </c>
       <c r="H309">
         <v>44130</v>
@@ -8872,7 +8894,7 @@
     </row>
     <row r="310" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G310" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="H310">
         <v>51720</v>
@@ -8880,7 +8902,7 @@
     </row>
     <row r="311" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G311" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="H311">
         <v>52790</v>
